--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdelrhman.gamal\Dar Al Riyadh\HTML\MBR-HTML\Map Visulaization\V06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{640AA39D-DDE0-4C3C-BD4B-5C27BB56A52E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E752CF6-33C6-4DEE-8C95-E9489230308D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -199,7 +199,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="247">
   <si>
     <t>DAR Projects Map Template - Full Populated Version</t>
   </si>
@@ -940,18 +940,6 @@
   </si>
   <si>
     <t>Below</t>
-  </si>
-  <si>
-    <t>R00000.00</t>
-  </si>
-  <si>
-    <t>Home</t>
-  </si>
-  <si>
-    <t>Egypt</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Ali+Sheha,+Atati,+Al+Haram,+Giza+Governorate,+Egypt/@29.9964437,31.1488939,721m/data=!3m2!1e3!4b1!4m6!3m5!1s0x145845c11bbbd527:0x762ad0335a4971ab!8m2!3d29.9964437!4d31.1514688!16s%2Fg%2F1tfhwl3q?entry=ttu&amp;g_ep=EgoyMDI2MDQwOC4wIKXMDSoASAFQAw%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -964,7 +952,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -999,20 +987,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1045,11 +1019,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1067,11 +1040,8 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
@@ -1113,8 +1083,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProjectsTemplate" displayName="ProjectsTemplate" ref="A1:R201">
-  <autoFilter ref="A1:R201" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProjectsTemplate" displayName="ProjectsTemplate" ref="A1:R200">
+  <autoFilter ref="A1:R200" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Project_Code"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Project_Name"/>
@@ -1598,7 +1568,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R201"/>
+  <dimension ref="A1:R200"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -3487,7 +3457,7 @@
         <v>46203</v>
       </c>
       <c r="M34" s="7">
-        <f t="shared" ref="M34:M65" si="2">IF(L34="","",YEAR(L34))</f>
+        <f t="shared" ref="M34:M64" si="2">IF(L34="","",YEAR(L34))</f>
         <v>2026</v>
       </c>
       <c r="N34" s="8">
@@ -3497,7 +3467,7 @@
         <v>0.1</v>
       </c>
       <c r="P34" s="7" t="str">
-        <f t="shared" ref="P34:P65" si="3">IF(O34="","",IF(O34&gt;0,"Ahead",IF(O34&lt;0,"Below","On Target")))</f>
+        <f t="shared" ref="P34:P64" si="3">IF(O34="","",IF(O34&gt;0,"Ahead",IF(O34&lt;0,"Below","On Target")))</f>
         <v>Ahead</v>
       </c>
       <c r="Q34" s="4" t="s">
@@ -4728,33 +4698,15 @@
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A58" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="B58" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E58" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="F58" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="G58" s="5">
-        <v>29.9964437</v>
-      </c>
-      <c r="H58" s="5">
-        <v>31.148893900000001</v>
-      </c>
-      <c r="I58" s="14" t="s">
-        <v>250</v>
-      </c>
+      <c r="A58" s="4"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="4"/>
       <c r="J58" s="6"/>
       <c r="K58" s="6"/>
       <c r="L58" s="6"/>
@@ -4941,13 +4893,13 @@
       <c r="K65" s="6"/>
       <c r="L65" s="6"/>
       <c r="M65" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="M65:M96" si="4">IF(L65="","",YEAR(L65))</f>
         <v/>
       </c>
       <c r="N65" s="8"/>
       <c r="O65" s="9"/>
       <c r="P65" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="P65:P96" si="5">IF(O65="","",IF(O65&gt;0,"Ahead",IF(O65&lt;0,"Below","On Target")))</f>
         <v/>
       </c>
       <c r="Q65" s="4"/>
@@ -4967,13 +4919,13 @@
       <c r="K66" s="6"/>
       <c r="L66" s="6"/>
       <c r="M66" s="7" t="str">
-        <f t="shared" ref="M66:M97" si="4">IF(L66="","",YEAR(L66))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N66" s="8"/>
       <c r="O66" s="9"/>
       <c r="P66" s="7" t="str">
-        <f t="shared" ref="P66:P97" si="5">IF(O66="","",IF(O66&gt;0,"Ahead",IF(O66&lt;0,"Below","On Target")))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="Q66" s="4"/>
@@ -5773,13 +5725,13 @@
       <c r="K97" s="6"/>
       <c r="L97" s="6"/>
       <c r="M97" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="M97:M128" si="6">IF(L97="","",YEAR(L97))</f>
         <v/>
       </c>
       <c r="N97" s="8"/>
       <c r="O97" s="9"/>
       <c r="P97" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="P97:P128" si="7">IF(O97="","",IF(O97&gt;0,"Ahead",IF(O97&lt;0,"Below","On Target")))</f>
         <v/>
       </c>
       <c r="Q97" s="4"/>
@@ -5799,13 +5751,13 @@
       <c r="K98" s="6"/>
       <c r="L98" s="6"/>
       <c r="M98" s="7" t="str">
-        <f t="shared" ref="M98:M129" si="6">IF(L98="","",YEAR(L98))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N98" s="8"/>
       <c r="O98" s="9"/>
       <c r="P98" s="7" t="str">
-        <f t="shared" ref="P98:P129" si="7">IF(O98="","",IF(O98&gt;0,"Ahead",IF(O98&lt;0,"Below","On Target")))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="Q98" s="4"/>
@@ -6605,13 +6557,13 @@
       <c r="K129" s="6"/>
       <c r="L129" s="6"/>
       <c r="M129" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="M129:M160" si="8">IF(L129="","",YEAR(L129))</f>
         <v/>
       </c>
       <c r="N129" s="8"/>
       <c r="O129" s="9"/>
       <c r="P129" s="7" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="P129:P160" si="9">IF(O129="","",IF(O129&gt;0,"Ahead",IF(O129&lt;0,"Below","On Target")))</f>
         <v/>
       </c>
       <c r="Q129" s="4"/>
@@ -6631,13 +6583,13 @@
       <c r="K130" s="6"/>
       <c r="L130" s="6"/>
       <c r="M130" s="7" t="str">
-        <f t="shared" ref="M130:M161" si="8">IF(L130="","",YEAR(L130))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="N130" s="8"/>
       <c r="O130" s="9"/>
       <c r="P130" s="7" t="str">
-        <f t="shared" ref="P130:P161" si="9">IF(O130="","",IF(O130&gt;0,"Ahead",IF(O130&lt;0,"Below","On Target")))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q130" s="4"/>
@@ -7437,13 +7389,13 @@
       <c r="K161" s="6"/>
       <c r="L161" s="6"/>
       <c r="M161" s="7" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="M161:M192" si="10">IF(L161="","",YEAR(L161))</f>
         <v/>
       </c>
       <c r="N161" s="8"/>
       <c r="O161" s="9"/>
       <c r="P161" s="7" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="P161:P192" si="11">IF(O161="","",IF(O161&gt;0,"Ahead",IF(O161&lt;0,"Below","On Target")))</f>
         <v/>
       </c>
       <c r="Q161" s="4"/>
@@ -7463,13 +7415,13 @@
       <c r="K162" s="6"/>
       <c r="L162" s="6"/>
       <c r="M162" s="7" t="str">
-        <f t="shared" ref="M162:M193" si="10">IF(L162="","",YEAR(L162))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N162" s="8"/>
       <c r="O162" s="9"/>
       <c r="P162" s="7" t="str">
-        <f t="shared" ref="P162:P193" si="11">IF(O162="","",IF(O162&gt;0,"Ahead",IF(O162&lt;0,"Below","On Target")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="Q162" s="4"/>
@@ -8269,13 +8221,13 @@
       <c r="K193" s="6"/>
       <c r="L193" s="6"/>
       <c r="M193" s="7" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="M193:M200" si="12">IF(L193="","",YEAR(L193))</f>
         <v/>
       </c>
       <c r="N193" s="8"/>
       <c r="O193" s="9"/>
       <c r="P193" s="7" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="P193:P200" si="13">IF(O193="","",IF(O193&gt;0,"Ahead",IF(O193&lt;0,"Below","On Target")))</f>
         <v/>
       </c>
       <c r="Q193" s="4"/>
@@ -8295,13 +8247,13 @@
       <c r="K194" s="6"/>
       <c r="L194" s="6"/>
       <c r="M194" s="7" t="str">
-        <f t="shared" ref="M194:M225" si="12">IF(L194="","",YEAR(L194))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="N194" s="8"/>
       <c r="O194" s="9"/>
       <c r="P194" s="7" t="str">
-        <f t="shared" ref="P194:P225" si="13">IF(O194="","",IF(O194&gt;0,"Ahead",IF(O194&lt;0,"Below","On Target")))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="Q194" s="4"/>
@@ -8463,34 +8415,8 @@
       <c r="Q200" s="4"/>
       <c r="R200" s="4"/>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A201" s="4"/>
-      <c r="B201" s="4"/>
-      <c r="C201" s="4"/>
-      <c r="D201" s="4"/>
-      <c r="E201" s="4"/>
-      <c r="F201" s="4"/>
-      <c r="G201" s="5"/>
-      <c r="H201" s="5"/>
-      <c r="I201" s="4"/>
-      <c r="J201" s="6"/>
-      <c r="K201" s="6"/>
-      <c r="L201" s="6"/>
-      <c r="M201" s="7" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="N201" s="8"/>
-      <c r="O201" s="9"/>
-      <c r="P201" s="7" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="Q201" s="4"/>
-      <c r="R201" s="4"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="P2:P201">
+  <conditionalFormatting sqref="P2:P200">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Ahead"</formula>
     </cfRule>
@@ -8501,13 +8427,10 @@
       <formula>"Below"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="I58" r:id="rId1" display="https://www.google.com/maps/place/Ali+Sheha,+Atati,+Al+Haram,+Giza+Governorate,+Egypt/@29.9964437,31.1488939,721m/data=!3m2!1e3!4b1!4m6!3m5!1s0x145845c11bbbd527:0x762ad0335a4971ab!8m2!3d29.9964437!4d31.1514688!16s%2Fg%2F1tfhwl3q?entry=ttu&amp;g_ep=EgoyMDI2MDQwOC4wIKXMDSoASAFQAw%3D%3D" xr:uid="{49EEFF4F-AB81-4F99-97F8-E19F2ED18EE9}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -8516,13 +8439,13 @@
           <x14:formula1>
             <xm:f>Lists!$A$2:$A$3</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C201</xm:sqref>
+          <xm:sqref>C2:C200</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000001000000}">
           <x14:formula1>
             <xm:f>Lists!$B$2:$B$7</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D201</xm:sqref>
+          <xm:sqref>D2:D200</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
